--- a/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
+++ b/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Внедрение ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Внедрение ИС как проект: от обследования и настройки до опытной эксплуатации и передачи в сопровождение. Студент разберёт этапы, роли участников и типичные точки отказа.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Внедрение ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">внедрение, жизненный цикл проекта, заказчик, интегратор, опытная эксплуатация</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Обследование»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент собирает сведения об организации: интервью с сотрудниками, наблюдение за рабочими местами, анализ документов. Результат: карта процессов и перечень проблем, оформленные в отчёт.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обследование</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t xml:space="preserve">интервью, наблюдение, карта процессов, источники сведений, отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -255,16 +255,16 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Стратегии внедрения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сравнение последовательного, параллельного, пилотного и поэтапного внедрения: когда каждый вариант уместен, сколько он стоит и чем рискует организация при переходе.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стратегии внедрения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">последовательное внедрение, параллельное внедрение, пилот, поэтапный запуск, риск перехода</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Gap-анализ»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент сравнивает текущие процессы организации с целевыми и находит разрывы: чего не хватает в данных, функциях и регламентах. Результат: таблица разрывов с приоритетами и способами закрытия.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gap-анализ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">текущее состояние, целевое состояние, разрыв, приоритет, способ закрытия</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Обследование организации»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Методы обследования: интервью, анкетирование, наблюдение, анализ документов и статистики. Студент учится выбирать метод под задачу и не собирать лишние данные.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обследование организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t xml:space="preserve">интервью, анкетирование, наблюдение, анализ документов, выборка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Требования и gap-анализ»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Как из сведений обследования получаются требования: функциональные, нефункциональные и ограничения. Студент разберёт, чем требование отличается от пожелания и как его проверить.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Требования и gap-анализ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t xml:space="preserve">функциональное требование, нефункциональное требование, ограничение, критерий проверки, трассировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -375,16 +375,16 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: План внедрения; Настройка.</t>
+          <t xml:space="preserve">Студент составляет план внедрения с этапами, сроками и ответственными, затем настраивает учебную ИС под требования: роли, справочники, маршруты. Сдаёт план и протокол настройки.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">План внедрения, Настройка</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">веха, план работ, роль, справочник, маршрут обработки</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -405,12 +405,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «План внедрения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">План внедрения связывает работы, сроки, ресурсы и зависимости. Студент разберёт критический путь, резерв времени и порядок, в котором работы можно двигать без срыва даты.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">План внедрения</t>
+          <t xml:space="preserve">работа, зависимость, критический путь, резерв времени, веха</t>
         </is>
       </c>
     </row>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Настройка ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Настройка ИС без изменения кода: организационная структура, роли и права, справочники, маршруты согласования, шаблоны документов и уведомления.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Настройка ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t xml:space="preserve">параметризация, права доступа, справочник, маршрут согласования, шаблон документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11-12</t>
@@ -465,16 +465,16 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Миграция; Импорт JSON.</t>
+          <t xml:space="preserve">Студент переносит данные из старой базы в новую: готовит выгрузку, чистит её, загружает JSON через импорт и сверяет количество и суммы. Сдаёт скрипт импорта и протокол сверки.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция, Импорт JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t xml:space="preserve">выгрузка, преобразование, импорт, ошибка импорта, сверка</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Миграция данных»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Миграция данных как управляемый процесс: инвентаризация, очистка, преобразование, загрузка и сверка. Студент увидит, где теряются записи и как откатить неудачный перенос.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t xml:space="preserve">инвентаризация, очистка данных, маппинг полей, контрольная сумма, откат</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Импорт JSON/CSV»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Форматы обмена JSON и CSV, их структура и ограничения. Студент разберёт разбор файла, проверку типов полей, обработку пропусков и повторный запуск импорта без дублей.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Импорт JSON/CSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t xml:space="preserve">JSON, CSV, схема данных, валидация, идемпотентность</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15-16</t>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Интеграция; Тестирование.</t>
+          <t xml:space="preserve">Студент настраивает обмен между учебной ИС и внешним сервисом, затем проверяет его тестами: успешный обмен, отказ сервиса, неверные данные. Сдаёт схему обмена и протокол тестов.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интеграция, Тестирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">точка интеграции, запрос, ответ, тест-кейс, журнал обмена</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Интеграция»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Способы связать ИС с другими системами: файловый обмен, API, очередь сообщений, шина. Студент разберёт, как выбирать способ и что делать при недоступности смежной системы.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интеграция</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">API, очередь сообщений, шина данных, формат обмена, повторная доставка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -615,16 +615,16 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Инструкция»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент пишет инструкцию для пользователя по одной операции учебной ИС: пошаговые действия, скриншоты, типичные ошибки. Сдаёт инструкцию, проверенную на коллеге по группе.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инструкция</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t xml:space="preserve">шаг операции, скриншот, типичная ошибка, глоссарий, проверка на читателе</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование при внедрении»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Виды тестирования при внедрении: модульное, интеграционное, приёмочное, нагрузочное. Студент разберёт, что проверяет каждый уровень и как оформить найденный дефект.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование при внедрении</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">тест-кейс, дефект, регрессия, нагрузочный тест, критерий приёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Обучение»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент готовит и проводит занятие для группы пользователей: программа, раздаточный материал, практическое упражнение. Сдаёт план занятия и лист обратной связи.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обучение</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t xml:space="preserve">программа обучения, роль пользователя, упражнение, обратная связь, раздаточный материал</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Обучение пользователей»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Обучение как часть внедрения: группы по ролям, форматы занятий, материалы и оценка усвоения. Студент разберёт, почему пользователи сопротивляются и как снять страх перед системой.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обучение пользователей</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t xml:space="preserve">группа обучения, формат занятия, усвоение, сопротивление, наставник</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -735,16 +735,16 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Документация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Комплект документации внедрения: руководство пользователя, администратора, регламент работы, программа обучения. Студент разберёт состав комплекта и требования к актуальности.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Документация</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+          <t xml:space="preserve">руководство пользователя, руководство администратора, регламент, версия, актуализация</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23-24</t>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Приёмка; Опытная эксплуатация.</t>
+          <t xml:space="preserve">Студент проводит приёмочные испытания учебной ИС по программе, фиксирует результаты и оформляет акт. Затем запускает опытную эксплуатацию с ограниченной группой и собирает замечания.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Приёмка, Опытная эксплуатация</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t xml:space="preserve">программа испытаний, акт приёмки, замечание, ограниченная группа, журнал опытной эксплуатации</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Организационные изменения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">ИС меняет распределение работы между сотрудниками: часть операций исчезает, появляются новые. Студент разберёт, как описать изменения и снизить потери при переходе.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организационные изменения</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t xml:space="preserve">организационная структура, обязанность, рабочее место, переходный период, сопротивление</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">26</t>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Управление изменениями»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Запрос на изменение, его оценка, согласование и внедрение. Студент разберёт, как не потерять контроль над системой, когда требования меняются уже после запуска.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Управление изменениями</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t xml:space="preserve">запрос на изменение, оценка влияния, согласование, журнал изменений, откат</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27-28</t>
@@ -855,16 +855,16 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Сопровождение; Оценка эффективности.</t>
+          <t xml:space="preserve">Студент организует сопровождение учебной ИС: очередь обращений, сроки реакции, назначение исполнителей. Затем считает эффект внедрения по выбранным метрикам и оформляет отчёт.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сопровождение, Оценка эффективности</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t xml:space="preserve">обращение, срок реакции, исполнитель, метрика, эффект внедрения</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Риски внедрения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Риски проекта внедрения: срыв сроков, сопротивление, потеря данных, недоступность подрядчика. Студент разберёт оценку вероятности и ущерба и выбор мер реагирования.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Риски внедрения</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t xml:space="preserve">реестр рисков, вероятность, ущерб, мера реагирования, владелец риска</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -915,16 +915,16 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Безопасность»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу безопасности: учётные записи, пароли, права, журналы, резервные копии. Сдаёт заполненный чек-лист и перечень найденных слабых мест.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+          <t xml:space="preserve">учётная запись, парольная политика, избыточные права, журнал доступа, слабое место</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">31</t>
@@ -945,16 +945,16 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Приёмка»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Приёмка подтверждает, что система соответствует требованиям и готова к работе. Студент разберёт виды приёмки, состав комиссии, программу испытаний и документы, которые подписываются.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Приёмка</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t xml:space="preserve">комиссия, программа испытаний, протокол, акт, критерий готовности</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">32</t>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Резервное копирование»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент настраивает резервное копирование учебной базы: расписание, полные и разностные копии, хранение и проверка. Сдаёт настроенное расписание и отчёт о пробном восстановлении.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t xml:space="preserve">полная копия, разностная копия, расписание, целостность, пробное восстановление</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Опытная эксплуатация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Опытная эксплуатация проверяет систему на реальной работе с ограниченной группой. Студент разберёт порядок запуска, сбор замечаний, критерии выхода и переход к промышленной эксплуатации.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Опытная эксплуатация</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">опытный участок, замечание, критерий выхода, промышленная эксплуатация, журнал</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
@@ -1035,16 +1035,16 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Поддержка»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент обрабатывает поток обращений в учебной ИС: регистрирует, классифицирует, решает по базе знаний и закрывает. Сдаёт журнал обращений с отметками времени реакции и решения.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поддержка</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t xml:space="preserve">обращение, категория, приоритет, база знаний, закрытие заявки</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Сопровождение»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Сопровождение после запуска: регламент работ, распределение ответственности, плановые обновления и отчётность. Студент разберёт, чем сопровождение отличается от проекта внедрения.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сопровождение</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t xml:space="preserve">регламент, ответственный, плановые работы, окно обслуживания, отчётность</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1095,16 +1095,16 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Оценка эффективности»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Эффект внедрения измеряют до и после: время операции, число ошибок, стоимость обработки, удовлетворённость. Студент разберёт выбор метрик и расчёт по реальным данным.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка эффективности</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
+          <t xml:space="preserve">базовая линия, метрика, время операции, стоимость обработки, удовлетворённость</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">37-38</t>
@@ -1125,16 +1125,16 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Метрики; Документация.</t>
+          <t xml:space="preserve">Студент собирает метрики работы учебной ИС за период, строит сводку и готовит отчёт с выводами. Дополняет комплект документации разделом о порядке сбора метрик.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики, Документация</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t xml:space="preserve">журнал системы, сводка, график, период, раздел документации</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">39</t>
@@ -1155,16 +1155,16 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Безопасность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Защита ИС при внедрении: разграничение доступа, парольная политика, журналирование, защита каналов и резервных копий. Студент разберёт типовые ошибки настройки прав.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
+          <t xml:space="preserve">минимальные привилегии, аутентификация, журналирование, шифрование канала, защита копий</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">40</t>
@@ -1185,16 +1185,16 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Защита»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студент защищает проект внедрения: доклад о ходе работ, демонстрация настроенной системы, ответы на вопросы комиссии. Сдаёт презентацию и пояснительную записку.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t xml:space="preserve">доклад, демонстрация, сценарий показа, пояснительная записка, вопросы комиссии</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
@@ -1215,16 +1215,16 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Резервное копирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Стратегия резервного копирования: что копировать, как часто, где хранить и сколько держать. Студент разберёт полные, разностные и инкрементные копии, правило трёх копий и проверку восстановления.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Резервное копирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
+          <t xml:space="preserve">полная копия, инкрементная копия, глубина хранения, внешнее хранилище, проверка восстановления</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
@@ -1245,16 +1245,16 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Поддержка пользователей»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Служба поддержки пользователей: каналы приёма, уровни поддержки, база знаний и показатели работы. Студент разберёт, как обращение проходит от первой линии до специалиста.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поддержка пользователей</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t xml:space="preserve">первая линия, вторая линия, канал приёма, эскалация, база знаний</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">43</t>
@@ -1275,16 +1275,16 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Метрики внедрения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Метрики проекта и метрики результата: соблюдение сроков, доля выполненных требований, число дефектов, время реакции поддержки. Студент разберёт, как не подменить результат активностью.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики внедрения</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
+          <t xml:space="preserve">метрика проекта, метрика результата, отклонение, дефект, план и факт</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">44</t>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Завершение проекта»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Завершение внедрения: передача системы в сопровождение, закрытие документов, разбор итогов и фиксация извлечённых уроков. Студент разберёт состав передаваемого комплекта.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Завершение проекта</t>
+          <t xml:space="preserve">передача в сопровождение, итоговый отчёт, извлечённые уроки, архив проекта, закрытие</t>
         </is>
       </c>
     </row>

--- a/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
+++ b/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D43" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D44" s="6">
-        <v>3960</v>
+        <v>88</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>

--- a/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
+++ b/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
@@ -212,12 +212,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Обследование</t>
+          <t xml:space="preserve">Лекция 2. Стратегии внедрения</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает сведения об организации: интервью с сотрудниками, наблюдение за рабочими местами, анализ документов. Результат: карта процессов и перечень проблем, оформленные в отчёт.</t>
+          <t xml:space="preserve">Сравнение последовательного, параллельного, пилотного и поэтапного внедрения: когда каждый вариант уместен, сколько он стоит и чем рискует организация при переходе.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">интервью, наблюдение, карта процессов, источники сведений, отчёт</t>
+          <t xml:space="preserve">последовательное внедрение, параллельное внедрение, пилот, поэтапный запуск, риск перехода</t>
         </is>
       </c>
     </row>
@@ -247,7 +247,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 2. Стратегии внедрения</t>
+          <t xml:space="preserve">Лекция 3. Обследование организации</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравнение последовательного, параллельного, пилотного и поэтапного внедрения: когда каждый вариант уместен, сколько он стоит и чем рискует организация при переходе.</t>
+          <t xml:space="preserve">Методы обследования: интервью, анкетирование, наблюдение, анализ документов и статистики. Студент учится выбирать метод под задачу и не собирать лишние данные.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">последовательное внедрение, параллельное внедрение, пилот, поэтапный запуск, риск перехода</t>
+          <t xml:space="preserve">интервью, анкетирование, наблюдение, анализ документов, выборка</t>
         </is>
       </c>
     </row>
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Gap-анализ</t>
+          <t xml:space="preserve">Практика 1. Обследование</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,12 +285,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент сравнивает текущие процессы организации с целевыми и находит разрывы: чего не хватает в данных, функциях и регламентах. Результат: таблица разрывов с приоритетами и способами закрытия.</t>
+          <t xml:space="preserve">Студент собирает сведения об организации: интервью с сотрудниками, наблюдение за рабочими местами, анализ документов. Результат: карта процессов и перечень проблем, оформленные в отчёт.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">текущее состояние, целевое состояние, разрыв, приоритет, способ закрытия</t>
+          <t xml:space="preserve">интервью, наблюдение, карта процессов, источники сведений, отчёт</t>
         </is>
       </c>
     </row>
@@ -307,7 +307,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Обследование организации</t>
+          <t xml:space="preserve">Лекция 4. Требования и gap-анализ</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Методы обследования: интервью, анкетирование, наблюдение, анализ документов и статистики. Студент учится выбирать метод под задачу и не собирать лишние данные.</t>
+          <t xml:space="preserve">Как из сведений обследования получаются требования: функциональные, нефункциональные и ограничения. Студент разберёт, чем требование отличается от пожелания и как его проверить.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">интервью, анкетирование, наблюдение, анализ документов, выборка</t>
+          <t xml:space="preserve">функциональное требование, нефункциональное требование, ограничение, критерий проверки, трассировка</t>
         </is>
       </c>
     </row>
@@ -332,12 +332,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Требования и gap-анализ</t>
+          <t xml:space="preserve">Практика 2. Gap-анализ</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,139 +345,139 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как из сведений обследования получаются требования: функциональные, нефункциональные и ограничения. Студент разберёт, чем требование отличается от пожелания и как его проверить.</t>
+          <t xml:space="preserve">Студент сравнивает текущие процессы организации с целевыми и находит разрывы: чего не хватает в данных, функциях и регламентах. Результат: таблица разрывов с приоритетами и способами закрытия.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">функциональное требование, нефункциональное требование, ограничение, критерий проверки, трассировка</t>
+          <t xml:space="preserve">текущее состояние, целевое состояние, разрыв, приоритет, способ закрытия</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 5. План внедрения</t>
+        </is>
+      </c>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">План внедрения связывает работы, сроки, ресурсы и зависимости. Студент разберёт критический путь, резерв времени и порядок, в котором работы можно двигать без срыва даты.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">работа, зависимость, критический путь, резерв времени, веха</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 6. Настройка ИС</t>
+        </is>
+      </c>
+      <c r="D13" s="6">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Настройка ИС без изменения кода: организационная структура, роли и права, справочники, маршруты согласования, шаблоны документов и уведомления.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">параметризация, права доступа, справочник, маршрут согласования, шаблон документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9-10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Практика 3. План внедрения; Настройка</t>
         </is>
       </c>
-      <c r="D12" s="6">
+      <c r="D14" s="6">
         <v>4</v>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студент составляет план внедрения с этапами, сроками и ответственными, затем настраивает учебную ИС под требования: роли, справочники, маршруты. Сдаёт план и протокол настройки.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">веха, план работ, роль, справочник, маршрут обработки</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 5. План внедрения</t>
-        </is>
-      </c>
-      <c r="D13" s="6">
-        <v>2</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">План внедрения связывает работы, сроки, ресурсы и зависимости. Студент разберёт критический путь, резерв времени и порядок, в котором работы можно двигать без срыва даты.</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">работа, зависимость, критический путь, резерв времени, веха</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 6. Настройка ИС</t>
-        </is>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Настройка ИС без изменения кода: организационная структура, роли и права, справочники, маршруты согласования, шаблоны документов и уведомления.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">параметризация, права доступа, справочник, маршрут согласования, шаблон документа</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Миграция; Импорт JSON</t>
+          <t xml:space="preserve">Лекция 7. Миграция данных</t>
         </is>
       </c>
       <c r="D15" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент переносит данные из старой базы в новую: готовит выгрузку, чистит её, загружает JSON через импорт и сверяет количество и суммы. Сдаёт скрипт импорта и протокол сверки.</t>
+          <t xml:space="preserve">Миграция данных как управляемый процесс: инвентаризация, очистка, преобразование, загрузка и сверка. Студент увидит, где теряются записи и как откатить неудачный перенос.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">выгрузка, преобразование, импорт, ошибка импорта, сверка</t>
+          <t xml:space="preserve">инвентаризация, очистка данных, маппинг полей, контрольная сумма, откат</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 7. Миграция данных</t>
+          <t xml:space="preserve">Лекция 8. Импорт JSON/CSV</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -495,79 +495,79 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция данных как управляемый процесс: инвентаризация, очистка, преобразование, загрузка и сверка. Студент увидит, где теряются записи и как откатить неудачный перенос.</t>
+          <t xml:space="preserve">Форматы обмена JSON и CSV, их структура и ограничения. Студент разберёт разбор файла, проверку типов полей, обработку пропусков и повторный запуск импорта без дублей.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">инвентаризация, очистка данных, маппинг полей, контрольная сумма, откат</t>
+          <t xml:space="preserve">JSON, CSV, схема данных, валидация, идемпотентность</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13-14</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Импорт JSON/CSV</t>
+          <t xml:space="preserve">Практика 4. Миграция; Импорт JSON</t>
         </is>
       </c>
       <c r="D17" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Форматы обмена JSON и CSV, их структура и ограничения. Студент разберёт разбор файла, проверку типов полей, обработку пропусков и повторный запуск импорта без дублей.</t>
+          <t xml:space="preserve">Студент переносит данные из старой базы в новую: готовит выгрузку, чистит её, загружает JSON через импорт и сверяет количество и суммы. Сдаёт скрипт импорта и протокол сверки.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON, CSV, схема данных, валидация, идемпотентность</t>
+          <t xml:space="preserve">выгрузка, преобразование, импорт, ошибка импорта, сверка</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Интеграция; Тестирование</t>
+          <t xml:space="preserve">Лекция 9. Интеграция</t>
         </is>
       </c>
       <c r="D18" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент настраивает обмен между учебной ИС и внешним сервисом, затем проверяет его тестами: успешный обмен, отказ сервиса, неверные данные. Сдаёт схему обмена и протокол тестов.</t>
+          <t xml:space="preserve">Способы связать ИС с другими системами: файловый обмен, API, очередь сообщений, шина. Студент разберёт, как выбирать способ и что делать при недоступности смежной системы.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">точка интеграции, запрос, ответ, тест-кейс, журнал обмена</t>
+          <t xml:space="preserve">API, очередь сообщений, шина данных, формат обмена, повторная доставка</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Интеграция</t>
+          <t xml:space="preserve">Лекция 10. Тестирование при внедрении</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,19 +585,19 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Способы связать ИС с другими системами: файловый обмен, API, очередь сообщений, шина. Студент разберёт, как выбирать способ и что делать при недоступности смежной системы.</t>
+          <t xml:space="preserve">Виды тестирования при внедрении: модульное, интеграционное, приёмочное, нагрузочное. Студент разберёт, что проверяет каждый уровень и как оформить найденный дефект.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">API, очередь сообщений, шина данных, формат обмена, повторная доставка</t>
+          <t xml:space="preserve">тест-кейс, дефект, регрессия, нагрузочный тест, критерий приёмки</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17-18</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -607,20 +607,20 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Инструкция</t>
+          <t xml:space="preserve">Практика 5. Интеграция; Тестирование</t>
         </is>
       </c>
       <c r="D20" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент пишет инструкцию для пользователя по одной операции учебной ИС: пошаговые действия, скриншоты, типичные ошибки. Сдаёт инструкцию, проверенную на коллеге по группе.</t>
+          <t xml:space="preserve">Студент настраивает обмен между учебной ИС и внешним сервисом, затем проверяет его тестами: успешный обмен, отказ сервиса, неверные данные. Сдаёт схему обмена и протокол тестов.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">шаг операции, скриншот, типичная ошибка, глоссарий, проверка на читателе</t>
+          <t xml:space="preserve">точка интеграции, запрос, ответ, тест-кейс, журнал обмена</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Тестирование при внедрении</t>
+          <t xml:space="preserve">Лекция 11. Обучение пользователей</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виды тестирования при внедрении: модульное, интеграционное, приёмочное, нагрузочное. Студент разберёт, что проверяет каждый уровень и как оформить найденный дефект.</t>
+          <t xml:space="preserve">Обучение как часть внедрения: группы по ролям, форматы занятий, материалы и оценка усвоения. Студент разберёт, почему пользователи сопротивляются и как снять страх перед системой.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">тест-кейс, дефект, регрессия, нагрузочный тест, критерий приёмки</t>
+          <t xml:space="preserve">группа обучения, формат занятия, усвоение, сопротивление, наставник</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Обучение</t>
+          <t xml:space="preserve">Практика 6. Обучение</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Обучение пользователей</t>
+          <t xml:space="preserve">Лекция 12. Документация</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обучение как часть внедрения: группы по ролям, форматы занятий, материалы и оценка усвоения. Студент разберёт, почему пользователи сопротивляются и как снять страх перед системой.</t>
+          <t xml:space="preserve">Комплект документации внедрения: руководство пользователя, администратора, регламент работы, программа обучения. Студент разберёт состав комплекта и требования к актуальности.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">группа обучения, формат занятия, усвоение, сопротивление, наставник</t>
+          <t xml:space="preserve">руководство пользователя, руководство администратора, регламент, версия, актуализация</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Документация</t>
+          <t xml:space="preserve">Практика 7. Инструкция</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,49 +735,49 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комплект документации внедрения: руководство пользователя, администратора, регламент работы, программа обучения. Студент разберёт состав комплекта и требования к актуальности.</t>
+          <t xml:space="preserve">Студент пишет инструкцию для пользователя по одной операции учебной ИС: пошаговые действия, скриншоты, типичные ошибки. Сдаёт инструкцию, проверенную на коллеге по группе.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">руководство пользователя, руководство администратора, регламент, версия, актуализация</t>
+          <t xml:space="preserve">шаг операции, скриншот, типичная ошибка, глоссарий, проверка на читателе</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Приёмка; Опытная эксплуатация</t>
+          <t xml:space="preserve">Лекция 13. Организационные изменения</t>
         </is>
       </c>
       <c r="D25" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проводит приёмочные испытания учебной ИС по программе, фиксирует результаты и оформляет акт. Затем запускает опытную эксплуатацию с ограниченной группой и собирает замечания.</t>
+          <t xml:space="preserve">ИС меняет распределение работы между сотрудниками: часть операций исчезает, появляются новые. Студент разберёт, как описать изменения и снизить потери при переходе.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">программа испытаний, акт приёмки, замечание, ограниченная группа, журнал опытной эксплуатации</t>
+          <t xml:space="preserve">организационная структура, обязанность, рабочее место, переходный период, сопротивление</t>
         </is>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Организационные изменения</t>
+          <t xml:space="preserve">Лекция 14. Управление изменениями</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -795,19 +795,19 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ИС меняет распределение работы между сотрудниками: часть операций исчезает, появляются новые. Студент разберёт, как описать изменения и снизить потери при переходе.</t>
+          <t xml:space="preserve">Запрос на изменение, его оценка, согласование и внедрение. Студент разберёт, как не потерять контроль над системой, когда требования меняются уже после запуска.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">организационная структура, обязанность, рабочее место, переходный период, сопротивление</t>
+          <t xml:space="preserve">запрос на изменение, оценка влияния, согласование, журнал изменений, откат</t>
         </is>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Управление изменениями</t>
+          <t xml:space="preserve">Лекция 15. Риски внедрения</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,49 +825,49 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрос на изменение, его оценка, согласование и внедрение. Студент разберёт, как не потерять контроль над системой, когда требования меняются уже после запуска.</t>
+          <t xml:space="preserve">Риски проекта внедрения: срыв сроков, сопротивление, потеря данных, недоступность подрядчика. Студент разберёт оценку вероятности и ущерба и выбор мер реагирования.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">запрос на изменение, оценка влияния, согласование, журнал изменений, откат</t>
+          <t xml:space="preserve">реестр рисков, вероятность, ущерб, мера реагирования, владелец риска</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-28</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Сопровождение; Оценка эффективности</t>
+          <t xml:space="preserve">Лекция 16. Приёмка</t>
         </is>
       </c>
       <c r="D28" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент организует сопровождение учебной ИС: очередь обращений, сроки реакции, назначение исполнителей. Затем считает эффект внедрения по выбранным метрикам и оформляет отчёт.</t>
+          <t xml:space="preserve">Приёмка подтверждает, что система соответствует требованиям и готова к работе. Студент разберёт виды приёмки, состав комиссии, программу испытаний и документы, которые подписываются.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">обращение, срок реакции, исполнитель, метрика, эффект внедрения</t>
+          <t xml:space="preserve">комиссия, программа испытаний, протокол, акт, критерий готовности</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Риски внедрения</t>
+          <t xml:space="preserve">Лекция 17. Опытная эксплуатация</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,19 +885,19 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Риски проекта внедрения: срыв сроков, сопротивление, потеря данных, недоступность подрядчика. Студент разберёт оценку вероятности и ущерба и выбор мер реагирования.</t>
+          <t xml:space="preserve">Опытная эксплуатация проверяет систему на реальной работе с ограниченной группой. Студент разберёт порядок запуска, сбор замечаний, критерии выхода и переход к промышленной эксплуатации.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">реестр рисков, вероятность, ущерб, мера реагирования, владелец риска</t>
+          <t xml:space="preserve">опытный участок, замечание, критерий выхода, промышленная эксплуатация, журнал</t>
         </is>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">28-29</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Безопасность</t>
+          <t xml:space="preserve">Практика 8. Приёмка; Опытная эксплуатация</t>
         </is>
       </c>
       <c r="D30" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу безопасности: учётные записи, пароли, права, журналы, резервные копии. Сдаёт заполненный чек-лист и перечень найденных слабых мест.</t>
+          <t xml:space="preserve">Студент проводит приёмочные испытания учебной ИС по программе, фиксирует результаты и оформляет акт. Затем запускает опытную эксплуатацию с ограниченной группой и собирает замечания.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">учётная запись, парольная политика, избыточные права, журнал доступа, слабое место</t>
+          <t xml:space="preserve">программа испытаний, акт приёмки, замечание, ограниченная группа, журнал опытной эксплуатации</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Приёмка</t>
+          <t xml:space="preserve">Лекция 18. Сопровождение</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,29 +945,29 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Приёмка подтверждает, что система соответствует требованиям и готова к работе. Студент разберёт виды приёмки, состав комиссии, программу испытаний и документы, которые подписываются.</t>
+          <t xml:space="preserve">Сопровождение после запуска: регламент работ, распределение ответственности, плановые обновления и отчётность. Студент разберёт, чем сопровождение отличается от проекта внедрения.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">комиссия, программа испытаний, протокол, акт, критерий готовности</t>
+          <t xml:space="preserve">регламент, ответственный, плановые работы, окно обслуживания, отчётность</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Резервное копирование</t>
+          <t xml:space="preserve">Лекция 19. Оценка эффективности</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,42 +975,42 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент настраивает резервное копирование учебной базы: расписание, полные и разностные копии, хранение и проверка. Сдаёт настроенное расписание и отчёт о пробном восстановлении.</t>
+          <t xml:space="preserve">Эффект внедрения измеряют до и после: время операции, число ошибок, стоимость обработки, удовлетворённость. Студент разберёт выбор метрик и расчёт по реальным данным.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">полная копия, разностная копия, расписание, целостность, пробное восстановление</t>
+          <t xml:space="preserve">базовая линия, метрика, время операции, стоимость обработки, удовлетворённость</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32-33</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Опытная эксплуатация</t>
+          <t xml:space="preserve">Практика 9. Сопровождение; Оценка эффективности</t>
         </is>
       </c>
       <c r="D33" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Опытная эксплуатация проверяет систему на реальной работе с ограниченной группой. Студент разберёт порядок запуска, сбор замечаний, критерии выхода и переход к промышленной эксплуатации.</t>
+          <t xml:space="preserve">Студент организует сопровождение учебной ИС: очередь обращений, сроки реакции, назначение исполнителей. Затем считает эффект внедрения по выбранным метрикам и оформляет отчёт.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">опытный участок, замечание, критерий выхода, промышленная эксплуатация, журнал</t>
+          <t xml:space="preserve">обращение, срок реакции, исполнитель, метрика, эффект внедрения</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Поддержка</t>
+          <t xml:space="preserve">Лекция 20. Безопасность</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент обрабатывает поток обращений в учебной ИС: регистрирует, классифицирует, решает по базе знаний и закрывает. Сдаёт журнал обращений с отметками времени реакции и решения.</t>
+          <t xml:space="preserve">Защита ИС при внедрении: разграничение доступа, парольная политика, журналирование, защита каналов и резервных копий. Студент разберёт типовые ошибки настройки прав.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">обращение, категория, приоритет, база знаний, закрытие заявки</t>
+          <t xml:space="preserve">минимальные привилегии, аутентификация, журналирование, шифрование канала, защита копий</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Сопровождение</t>
+          <t xml:space="preserve">Практика 10. Безопасность</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сопровождение после запуска: регламент работ, распределение ответственности, плановые обновления и отчётность. Студент разберёт, чем сопровождение отличается от проекта внедрения.</t>
+          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу безопасности: учётные записи, пароли, права, журналы, резервные копии. Сдаёт заполненный чек-лист и перечень найденных слабых мест.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">регламент, ответственный, плановые работы, окно обслуживания, отчётность</t>
+          <t xml:space="preserve">учётная запись, парольная политика, избыточные права, журнал доступа, слабое место</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 19. Оценка эффективности</t>
+          <t xml:space="preserve">Лекция 21. Резервное копирование</t>
         </is>
       </c>
       <c r="D36" s="6">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эффект внедрения измеряют до и после: время операции, число ошибок, стоимость обработки, удовлетворённость. Студент разберёт выбор метрик и расчёт по реальным данным.</t>
+          <t xml:space="preserve">Стратегия резервного копирования: что копировать, как часто, где хранить и сколько держать. Студент разберёт полные, разностные и инкрементные копии, правило трёх копий и проверку восстановления.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">базовая линия, метрика, время операции, стоимость обработки, удовлетворённость</t>
+          <t xml:space="preserve">полная копия, инкрементная копия, глубина хранения, внешнее хранилище, проверка восстановления</t>
         </is>
       </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">37-38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1117,27 +1117,27 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 13. Метрики; Документация</t>
+          <t xml:space="preserve">Практика 11. Резервное копирование</t>
         </is>
       </c>
       <c r="D37" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает метрики работы учебной ИС за период, строит сводку и готовит отчёт с выводами. Дополняет комплект документации разделом о порядке сбора метрик.</t>
+          <t xml:space="preserve">Студент настраивает резервное копирование учебной базы: расписание, полные и разностные копии, хранение и проверка. Сдаёт настроенное расписание и отчёт о пробном восстановлении.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">журнал системы, сводка, график, период, раздел документации</t>
+          <t xml:space="preserve">полная копия, разностная копия, расписание, целостность, пробное восстановление</t>
         </is>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 20. Безопасность</t>
+          <t xml:space="preserve">Лекция 22. Поддержка пользователей</t>
         </is>
       </c>
       <c r="D38" s="6">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита ИС при внедрении: разграничение доступа, парольная политика, журналирование, защита каналов и резервных копий. Студент разберёт типовые ошибки настройки прав.</t>
+          <t xml:space="preserve">Служба поддержки пользователей: каналы приёма, уровни поддержки, база знаний и показатели работы. Студент разберёт, как обращение проходит от первой линии до специалиста.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">минимальные привилегии, аутентификация, журналирование, шифрование канала, защита копий</t>
+          <t xml:space="preserve">первая линия, вторая линия, канал приёма, эскалация, база знаний</t>
         </is>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 14. Защита</t>
+          <t xml:space="preserve">Практика 12. Поддержка</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,19 +1185,19 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент защищает проект внедрения: доклад о ходе работ, демонстрация настроенной системы, ответы на вопросы комиссии. Сдаёт презентацию и пояснительную записку.</t>
+          <t xml:space="preserve">Студент обрабатывает поток обращений в учебной ИС: регистрирует, классифицирует, решает по базе знаний и закрывает. Сдаёт журнал обращений с отметками времени реакции и решения.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">доклад, демонстрация, сценарий показа, пояснительная записка, вопросы комиссии</t>
+          <t xml:space="preserve">обращение, категория, приоритет, база знаний, закрытие заявки</t>
         </is>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 21. Резервное копирование</t>
+          <t xml:space="preserve">Лекция 23. Метрики внедрения</t>
         </is>
       </c>
       <c r="D40" s="6">
@@ -1215,42 +1215,42 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стратегия резервного копирования: что копировать, как часто, где хранить и сколько держать. Студент разберёт полные, разностные и инкрементные копии, правило трёх копий и проверку восстановления.</t>
+          <t xml:space="preserve">Метрики проекта и метрики результата: соблюдение сроков, доля выполненных требований, число дефектов, время реакции поддержки. Студент разберёт, как не подменить результат активностью.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">полная копия, инкрементная копия, глубина хранения, внешнее хранилище, проверка восстановления</t>
+          <t xml:space="preserve">метрика проекта, метрика результата, отклонение, дефект, план и факт</t>
         </is>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">41-42</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 22. Поддержка пользователей</t>
+          <t xml:space="preserve">Практика 13. Метрики; Документация</t>
         </is>
       </c>
       <c r="D41" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Служба поддержки пользователей: каналы приёма, уровни поддержки, база знаний и показатели работы. Студент разберёт, как обращение проходит от первой линии до специалиста.</t>
+          <t xml:space="preserve">Студент собирает метрики работы учебной ИС за период, строит сводку и готовит отчёт с выводами. Дополняет комплект документации разделом о порядке сбора метрик.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">первая линия, вторая линия, канал приёма, эскалация, база знаний</t>
+          <t xml:space="preserve">журнал системы, сводка, график, период, раздел документации</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 23. Метрики внедрения</t>
+          <t xml:space="preserve">Лекция 24. Завершение проекта</t>
         </is>
       </c>
       <c r="D42" s="6">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики проекта и метрики результата: соблюдение сроков, доля выполненных требований, число дефектов, время реакции поддержки. Студент разберёт, как не подменить результат активностью.</t>
+          <t xml:space="preserve">Завершение внедрения: передача системы в сопровождение, закрытие документов, разбор итогов и фиксация извлечённых уроков. Студент разберёт состав передаваемого комплекта.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">метрика проекта, метрика результата, отклонение, дефект, план и факт</t>
+          <t xml:space="preserve">передача в сопровождение, итоговый отчёт, извлечённые уроки, архив проекта, закрытие</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 24. Завершение проекта</t>
+          <t xml:space="preserve">Практика 14. Защита</t>
         </is>
       </c>
       <c r="D43" s="6">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Завершение внедрения: передача системы в сопровождение, закрытие документов, разбор итогов и фиксация извлечённых уроков. Студент разберёт состав передаваемого комплекта.</t>
+          <t xml:space="preserve">Студент защищает проект внедрения: доклад о ходе работ, демонстрация настроенной системы, ответы на вопросы комиссии. Сдаёт презентацию и пояснительную записку.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">передача в сопровождение, итоговый отчёт, извлечённые уроки, архив проекта, закрытие</t>
+          <t xml:space="preserve">доклад, демонстрация, сценарий показа, пояснительная записка, вопросы комиссии</t>
         </is>
       </c>
     </row>

--- a/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
+++ b/courses/4/is-implementation/dist/Учебный_план_Внедрение_информационных_систем.xlsx
@@ -195,7 +195,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Внедрение ИС как проект: от обследования и настройки до опытной эксплуатации и передачи в сопровождение. Студент разберёт этапы, роли участников и типичные точки отказа.</t>
+          <t xml:space="preserve">Внедрение ИС как проект: от обследования и настройки до опытной эксплуатации и передачи в сопровождение. Вы разберёте этапы, роли участников и типичные точки отказа.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -255,7 +255,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Методы обследования: интервью, анкетирование, наблюдение, анализ документов и статистики. Студент учится выбирать метод под задачу и не собирать лишние данные.</t>
+          <t xml:space="preserve">Методы обследования: интервью, анкетирование, наблюдение, анализ документов и статистики. Вы учитесь выбирать метод под задачу и не собирать лишние данные.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -264,7 +264,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Обследование</t>
+          <t xml:space="preserve">Практика 1. Карта процессов и интервью</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,7 +285,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает сведения об организации: интервью с сотрудниками, наблюдение за рабочими местами, анализ документов. Результат: карта процессов и перечень проблем, оформленные в отчёт.</t>
+          <t xml:space="preserve">Сбор фактов о приёме заказа: план интервью, наблюдение, хронометраж и карта процесса. Результат: отчёт с перечнем проблем и подтверждающими данными.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как из сведений обследования получаются требования: функциональные, нефункциональные и ограничения. Студент разберёт, чем требование отличается от пожелания и как его проверить.</t>
+          <t xml:space="preserve">Как из сведений обследования получаются требования: функциональные, нефункциональные и ограничения. Вы разберёте, чем требование отличается от пожелания и как его проверить.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -324,7 +324,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -337,7 +337,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Gap-анализ</t>
+          <t xml:space="preserve">Практика 2. Таблица разрывов и приоритеты</t>
         </is>
       </c>
       <c r="D11" s="6">
@@ -345,7 +345,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент сравнивает текущие процессы организации с целевыми и находит разрывы: чего не хватает в данных, функциях и регламентах. Результат: таблица разрывов с приоритетами и способами закрытия.</t>
+          <t xml:space="preserve">Сравнение текущего и целевого процесса, разрывы в функциях, данных и регламентах. Результат: таблица разрывов с приоритетами и способами закрытия.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">План внедрения связывает работы, сроки, ресурсы и зависимости. Студент разберёт критический путь, резерв времени и порядок, в котором работы можно двигать без срыва даты.</t>
+          <t xml:space="preserve">План внедрения связывает работы, сроки, ресурсы и зависимости. Вы разберёте критический путь, резерв времени и порядок, в котором работы можно двигать без срыва даты.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. План внедрения; Настройка</t>
+          <t xml:space="preserve">Практика 3. Дорожная карта и рабочая среда</t>
         </is>
       </c>
       <c r="D14" s="6">
@@ -435,7 +435,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент составляет план внедрения с этапами, сроками и ответственными, затем настраивает учебную ИС под требования: роли, справочники, маршруты. Сдаёт план и протокол настройки.</t>
+          <t xml:space="preserve">Календарный план внедрения с этапами, сроками и ответственными, затем настройка ролей, справочников и маршрутов учебной ИС. Результат: дорожная карта и протокол настройки.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Миграция данных как управляемый процесс: инвентаризация, очистка, преобразование, загрузка и сверка. Студент увидит, где теряются записи и как откатить неудачный перенос.</t>
+          <t xml:space="preserve">Миграция данных как управляемый процесс: инвентаризация, очистка, преобразование, загрузка и сверка. Вы увидите, где теряются записи и как откатить неудачный перенос.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Форматы обмена JSON и CSV, их структура и ограничения. Студент разберёт разбор файла, проверку типов полей, обработку пропусков и повторный запуск импорта без дублей.</t>
+          <t xml:space="preserve">Форматы обмена JSON и CSV, их структура и ограничения. Вы разберёте разбор файла, проверку типов полей, обработку пропусков и повторный запуск импорта без дублей.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -504,7 +504,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13-14</t>
@@ -517,7 +517,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Миграция; Импорт JSON</t>
+          <t xml:space="preserve">Практика 4. Перенос справочников и сверка данных</t>
         </is>
       </c>
       <c r="D17" s="6">
@@ -525,7 +525,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент переносит данные из старой базы в новую: готовит выгрузку, чистит её, загружает JSON через импорт и сверяет количество и суммы. Сдаёт скрипт импорта и протокол сверки.</t>
+          <t xml:space="preserve">Выгрузка из старой базы, очистка, загрузка JSON и сверка количества и сумм. Результат: скрипт импорта и протокол сверки.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Способы связать ИС с другими системами: файловый обмен, API, очередь сообщений, шина. Студент разберёт, как выбирать способ и что делать при недоступности смежной системы.</t>
+          <t xml:space="preserve">Способы связать ИС с другими системами: файловый обмен, API, очередь сообщений, шина. Вы разберёте, как выбирать способ и что делать при недоступности смежной системы.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виды тестирования при внедрении: модульное, интеграционное, приёмочное, нагрузочное. Студент разберёт, что проверяет каждый уровень и как оформить найденный дефект.</t>
+          <t xml:space="preserve">Виды тестирования при внедрении: модульное, интеграционное, приёмочное, нагрузочное. Вы разберёте, что проверяет каждый уровень и как оформить найденный дефект.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Интеграция; Тестирование</t>
+          <t xml:space="preserve">Практика 5. Обмен с сайтом и проверка сценариев</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,7 +615,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент настраивает обмен между учебной ИС и внешним сервисом, затем проверяет его тестами: успешный обмен, отказ сервиса, неверные данные. Сдаёт схему обмена и протокол тестов.</t>
+          <t xml:space="preserve">Настройка обмена между учебной ИС и внешним сервисом, проверка успешного обмена, отказа сервиса и неверных данных. Результат: схема обмена и протокол тестов.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обучение как часть внедрения: группы по ролям, форматы занятий, материалы и оценка усвоения. Студент разберёт, почему пользователи сопротивляются и как снять страх перед системой.</t>
+          <t xml:space="preserve">Обучение как часть внедрения: группы по ролям, форматы занятий, материалы и оценка усвоения. Вы разберёте, почему пользователи сопротивляются и как снять страх перед системой.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Обучение</t>
+          <t xml:space="preserve">Практика 6. Программа занятия для кладовщиков</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,7 +675,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент готовит и проводит занятие для группы пользователей: программа, раздаточный материал, практическое упражнение. Сдаёт план занятия и лист обратной связи.</t>
+          <t xml:space="preserve">Подготовка и проведение занятия для роли кладовщика: программа, раздаточный материал и упражнение на учебной ИС. Результат: план занятия и лист обратной связи.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комплект документации внедрения: руководство пользователя, администратора, регламент работы, программа обучения. Студент разберёт состав комплекта и требования к актуальности.</t>
+          <t xml:space="preserve">Комплект документации внедрения: руководство пользователя, администратора, регламент работы, программа обучения. Вы разберёте состав комплекта и требования к актуальности.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -727,7 +727,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Инструкция</t>
+          <t xml:space="preserve">Практика 7. Памятка по приёмке накладной</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,7 +735,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент пишет инструкцию для пользователя по одной операции учебной ИС: пошаговые действия, скриншоты, типичные ошибки. Сдаёт инструкцию, проверенную на коллеге по группе.</t>
+          <t xml:space="preserve">Пошаговая инструкция по одной операции учебной ИС: действия, скриншоты и типичные ошибки. Результат: памятка, проверенная на коллеге.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ИС меняет распределение работы между сотрудниками: часть операций исчезает, появляются новые. Студент разберёт, как описать изменения и снизить потери при переходе.</t>
+          <t xml:space="preserve">ИС меняет распределение работы между сотрудниками: часть операций исчезает, появляются новые. Вы разберёте, как описать изменения и снизить потери при переходе.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Запрос на изменение, его оценка, согласование и внедрение. Студент разберёт, как не потерять контроль над системой, когда требования меняются уже после запуска.</t>
+          <t xml:space="preserve">Запрос на изменение, его оценка, согласование и внедрение. Вы разберёте, как не потерять контроль над системой, когда требования меняются уже после запуска.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Риски проекта внедрения: срыв сроков, сопротивление, потеря данных, недоступность подрядчика. Студент разберёт оценку вероятности и ущерба и выбор мер реагирования.</t>
+          <t xml:space="preserve">Риски проекта внедрения: срыв сроков, сопротивление, потеря данных, недоступность подрядчика. Вы разберёте оценку вероятности и ущерба и выбор мер реагирования.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Приёмка подтверждает, что система соответствует требованиям и готова к работе. Студент разберёт виды приёмки, состав комиссии, программу испытаний и документы, которые подписываются.</t>
+          <t xml:space="preserve">Приёмка подтверждает, что система соответствует требованиям и готова к работе. Вы разберёте виды приёмки, состав комиссии, программу испытаний и документы, которые подписываются.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Опытная эксплуатация проверяет систему на реальной работе с ограниченной группой. Студент разберёт порядок запуска, сбор замечаний, критерии выхода и переход к промышленной эксплуатации.</t>
+          <t xml:space="preserve">Опытная эксплуатация проверяет систему на реальной работе с ограниченной группой. Вы разберёте порядок запуска, сбор замечаний, критерии выхода и переход к промышленной эксплуатации.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Приёмка; Опытная эксплуатация</t>
+          <t xml:space="preserve">Практика 8. Программа испытаний и пилотный запуск</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,7 +915,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проводит приёмочные испытания учебной ИС по программе, фиксирует результаты и оформляет акт. Затем запускает опытную эксплуатацию с ограниченной группой и собирает замечания.</t>
+          <t xml:space="preserve">Приёмочные испытания учебной ИС по программе, протокол и акт, затем опытная эксплуатация с ограниченной группой и сбор замечаний. Результат: комплект документов пилота.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сопровождение после запуска: регламент работ, распределение ответственности, плановые обновления и отчётность. Студент разберёт, чем сопровождение отличается от проекта внедрения.</t>
+          <t xml:space="preserve">Сопровождение после запуска: регламент работ, распределение ответственности, плановые обновления и отчётность. Вы разберёте, чем сопровождение отличается от проекта внедрения.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эффект внедрения измеряют до и после: время операции, число ошибок, стоимость обработки, удовлетворённость. Студент разберёт выбор метрик и расчёт по реальным данным.</t>
+          <t xml:space="preserve">Эффект внедрения измеряют до и после: время операции, число ошибок, стоимость обработки, удовлетворённость. Вы разберёте выбор метрик и расчёт по реальным данным.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Сопровождение; Оценка эффективности</t>
+          <t xml:space="preserve">Практика 9. Очередь обращений и расчёт эффекта</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент организует сопровождение учебной ИС: очередь обращений, сроки реакции, назначение исполнителей. Затем считает эффект внедрения по выбранным метрикам и оформляет отчёт.</t>
+          <t xml:space="preserve">Организация сопровождения учебной ИС: очередь обращений, сроки реакции и назначение исполнителей, затем расчёт эффекта внедрения по метрикам. Результат: регламент и отчёт.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита ИС при внедрении: разграничение доступа, парольная политика, журналирование, защита каналов и резервных копий. Студент разберёт типовые ошибки настройки прав.</t>
+          <t xml:space="preserve">Защита ИС при внедрении: разграничение доступа, парольная политика, журналирование, защита каналов и резервных копий. Вы разберёте типовые ошибки настройки прав.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1044,7 +1044,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Безопасность</t>
+          <t xml:space="preserve">Практика 10. Аудит учётных записей и прав</t>
         </is>
       </c>
       <c r="D35" s="6">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент проверяет учебную ИС по чек-листу безопасности: учётные записи, пароли, права, журналы, резервные копии. Сдаёт заполненный чек-лист и перечень найденных слабых мест.</t>
+          <t xml:space="preserve">Проверка учебной ИС по чек-листу безопасности: учётные записи, пароли, права, журналы и резервные копии. Результат: чек-лист и перечень слабых мест.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стратегия резервного копирования: что копировать, как часто, где хранить и сколько держать. Студент разберёт полные, разностные и инкрементные копии, правило трёх копий и проверку восстановления.</t>
+          <t xml:space="preserve">Стратегия резервного копирования: что копировать, как часто, где хранить и сколько держать. Вы разберёте полные, разностные и инкрементные копии, правило трёх копий и проверку восстановления.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Резервное копирование</t>
+          <t xml:space="preserve">Практика 11. Расписание копий и пробное восстановление</t>
         </is>
       </c>
       <c r="D37" s="6">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент настраивает резервное копирование учебной базы: расписание, полные и разностные копии, хранение и проверка. Сдаёт настроенное расписание и отчёт о пробном восстановлении.</t>
+          <t xml:space="preserve">Настройка расписания полных и разностных копий учебной базы, проверка целостности и восстановление в отдельную базу. Результат: расписание и отчёт о восстановлении.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Служба поддержки пользователей: каналы приёма, уровни поддержки, база знаний и показатели работы. Студент разберёт, как обращение проходит от первой линии до специалиста.</t>
+          <t xml:space="preserve">Служба поддержки пользователей: каналы приёма, уровни поддержки, база знаний и показатели работы. Вы разберёте, как обращение проходит от первой линии до специалиста.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Поддержка</t>
+          <t xml:space="preserve">Практика 12. Обработка потока обращений</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент обрабатывает поток обращений в учебной ИС: регистрирует, классифицирует, решает по базе знаний и закрывает. Сдаёт журнал обращений с отметками времени реакции и решения.</t>
+          <t xml:space="preserve">Регистрация, классификация и решение обращений по базе знаний, эскалация и закрытие с подтверждением. Результат: журнал обращений с отметками времени.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метрики проекта и метрики результата: соблюдение сроков, доля выполненных требований, число дефектов, время реакции поддержки. Студент разберёт, как не подменить результат активностью.</t>
+          <t xml:space="preserve">Метрики проекта и метрики результата: соблюдение сроков, доля выполненных требований, число дефектов, время реакции поддержки. Вы разберёте, как не подменить результат активностью.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 13. Метрики; Документация</t>
+          <t xml:space="preserve">Практика 13. Сводка метрик и раздел регламента</t>
         </is>
       </c>
       <c r="D41" s="6">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент собирает метрики работы учебной ИС за период, строит сводку и готовит отчёт с выводами. Дополняет комплект документации разделом о порядке сбора метрик.</t>
+          <t xml:space="preserve">Сбор метрик работы учебной ИС за период, сводка и график, дополнение комплекта документации разделом о сборе метрик. Результат: отчёт и раздел регламента.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Завершение внедрения: передача системы в сопровождение, закрытие документов, разбор итогов и фиксация извлечённых уроков. Студент разберёт состав передаваемого комплекта.</t>
+          <t xml:space="preserve">Завершение внедрения: передача системы в сопровождение, закрытие документов, разбор итогов и фиксация извлечённых уроков. Вы разберёте состав передаваемого комплекта.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 14. Защита</t>
+          <t xml:space="preserve">Практика 14. Защита проекта внедрения</t>
         </is>
       </c>
       <c r="D43" s="6">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студент защищает проект внедрения: доклад о ходе работ, демонстрация настроенной системы, ответы на вопросы комиссии. Сдаёт презентацию и пояснительную записку.</t>
+          <t xml:space="preserve">Итоговая защита: доклад о ходе работ, демонстрация системы по сценарию, пояснительная записка и ответы на вопросы комиссии. Результат: презентация и комплект документов.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
